--- a/Semantic Analysis Results/Cosine Similarity/Kualitatif/Evaluasi 2 Ahli B.xlsx
+++ b/Semantic Analysis Results/Cosine Similarity/Kualitatif/Evaluasi 2 Ahli B.xlsx
@@ -70,23 +70,12 @@
 5 - Sangat Baik: Terjemahan berhasil mempertahankan konteks, kiasan, dan nuansa makna dari ayat asli dengan sangat baik.</t>
       </text>
     </comment>
-    <comment authorId="0" ref="C32">
-      <text>
-        <t xml:space="preserve">Jika Anda menemukan perbedaan atau penyimpangan makna pada terjemahan Google Translate, mohon deskripsikan sifat penyimpangan tersebut. Mohon berikan contoh spesifik dari teks dan klasifikasikan (contoh: reduksi makna, penambahan makna, distorsi, terjemahan terlalu harfiah, atau kategori lain yang Anda identifikasi).
-jika tidak ada, silakan kosongkan saja</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="C33">
-      <text>
-        <t xml:space="preserve">Silakan berikan analisis, komentar, atau catatan lain yang Anda anggap penting terkait perbandingan terjemahan untuk ayat ini.</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="234">
   <si>
     <t>Chapter</t>
   </si>
@@ -115,6 +104,15 @@
     <t>Seberapa baik Google Translate mempertahankan makna kontekstual, nuansa (misalnya kiasan, metafora), atau penekanan retoris dari ayat tersebut?</t>
   </si>
   <si>
+    <t>Fahd - Google</t>
+  </si>
+  <si>
+    <t>Kemenag - Google</t>
+  </si>
+  <si>
+    <t>Fahd - Kemenag</t>
+  </si>
+  <si>
     <t>Pewarna Allah, dan siapakah yang lebih baik dari Allah dalam hal pewarnaan? Dan kita adalah hamba-hamba-Nya.</t>
   </si>
   <si>
@@ -122,6 +120,174 @@
   </si>
   <si>
     <t>Ṣibgah Allah.  Dan siapakah yang lebih baik Ṣibgah-nya daripada Allah? Dan hanya kepada-Nya-lah kami menyembah.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Terjemahan versi Google Translate cukup setara secara makna inti, namun kurang akurat secara istilah dan konteks. Kalimat </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Pewarna Allah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> tidak cocok dipakaikan pada konteks ayat ini. Kemenag memilih tidak menterjemahkan sama sekali ayat ini.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Terjemahan versi Google Translate cukup setara secara makna inti, namun terasa kurang akurat secara istilah dan konteks. Kalimat </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Pewarna Allah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> tidak cocok dipakaikan pada konteks ayat ini. Sementara itu, King Fahd mempertahankan istilah khas dalam bentuk transliterasi </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>"Ṣibgah"</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, yang lebih tepat untuk mengacu pada konsep teologis yang khas dalam ayat ini.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Dalam ayat ini, Google Translate kurang akurat dalam menerjemahkan istilah teologis </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>ṣibgah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> yang mengandung makna mendalam tentang identitas keimanan atau agama Allah. Kata </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Pewarna Allah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> terdengar literal dan tidak mewakili kedalaman makna </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>ṣibgah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> dalam tradisi Islam. Sedangkan Kemenag dan King Fahd memilih untuk tidak menerjemahkan langsung,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google Translate gagal menangkap nuansa kiasan dan keindahan retoris dari kata ṣibgah, yang dalam tafsir bermakna </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>agama Allah, fitrah, atau tanda khas keimanan</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">. Metafora pewarnaan dalam konteks ini mengandung makna kontekstual yang tidak bisa diwakili begitu saja dengan kata </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>pewarna</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> secara tekstual.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.39719975</t>
+  </si>
+  <si>
+    <t>0.39511508</t>
+  </si>
+  <si>
+    <t>0.98528296</t>
   </si>
   <si>
     <t>Dan mereka berencana, dan Allah pun berencana. Dan Allah adalah sebaik-baik perencana.</t>
@@ -133,6 +299,158 @@
     <t>Orang-orang kafir itu membuat tipu daya, dan Allah membalas tipu daya mereka itu.  Dan Allah sebaik-baik pembalas tipu daya.</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Makna dari Google Translate sudah setara dengan makna yang diberikan Kemenag, namun Google kehilangan konteks rencana yang dibicarakan di ayat ini karena tidak memuat makna </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>rencana</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> dengan rencana jahat. Sedangkan dalam terjemahan Kemenag rencana tadi diterjemahkan langsung dengan kalimat </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>membuat tipu daya.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google Translate menyampaikan makna inti secara umum—yakni adanya </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>rencana</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> dari orang kafir dan tanggapan dari Allah. Versi King Fahd lebih akurat secara makna dan nuansa, karena menyebutkan secara eksplisit bahwa yang dimaksud adalah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>tipu daya</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Kurang akurat. Istilah makr dalam konteks ayat ini berarti tipu daya atau strategi tersembunyi untuk mencelakakan, bukan sekadar </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“rencana”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">. Google Translate menerjemahkannya menjadi </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“berencana”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, yang bisa bermakna netral atau bahkan positif, padahal maksud ayat adalah tipu muslihat negatif.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google Translate kurang menangkap nuansa negatif dari kata </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>makr</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">, serta tidak menampilkan keadilan dan keperkasaan Allah dalam </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“membalas tipu daya”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> secara setimpal.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.4138204</t>
+  </si>
+  <si>
+    <t>0.4426761</t>
+  </si>
+  <si>
+    <t>0.9654912</t>
+  </si>
+  <si>
     <t>Mereka meminta pendapat hukum kepadamu. Katakanlah, "Allah memberimu pendapat hukum tentang orang-orang yang belum mewarisi. Jika seorang laki-laki meninggal dunia dan tidak meninggalkan anak kecuali seorang saudara perempuan, maka saudara perempuannya berhak atas separuh dari harta warisan yang ditinggalkannya, dan laki-laki berhak mewarisi darinya jika ia tidak meninggalkan anak. Jika ada dua saudara perempuan, maka mereka berhak atas dua pertiga dari harta warisan yang ditinggalkannya. Jika ada saudara laki-laki dan saudara perempuan, maka laki-laki berhak atas bagian dari satu saudara perempuan. Dan dua perempuan. Allah menjelaskannya kepadamu, agar kamu tidak tersesat. Dan Allah Maha Mengetahui segala sesuatu.</t>
   </si>
   <si>
@@ -140,6 +458,173 @@
   </si>
   <si>
     <t>Mereka meminta fatwa kepadamu (tentang kalālah). Katakanlah, "Allah memberi fatwa kepadamu tentang kalālah (yaitu), jika seorang meninggal dunia, dan ia tidak mempunyai anak dan mempunyai saudara perempuan, maka bagi saudaranya yang perempuan itu seperdua dari harta yang ditinggalkannya, dan saudaranya yang laki-laki mempusakai (seluruh harta saudara perempuan), jika ia tidak mempunyai anak; tetapi jika saudara perempuan itu dua orang, maka bagi keduanya dua pertiga dari harta yang ditinggalkan oleh yang meninggal.  Dan jika mereka (ahli waris itu terdiri dari) saudara-saudara laki dan perempuan, maka bagian seorang saudara laki-laki sebanyak bagian dua orang saudara perempuan".  Allah menerangkan (hukum ini) kepadamu, supaya kamu tidak sesat.  Dan Allah Maha Mengetahui segala sesuatu.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google menerjemahkan bagian-bagian penting ayat ini secara umum, tetapi ada ketidaksesuaian secara struktur dan istilah. Misalnya, istilah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>kalālah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> tidak muncul sama sekali, padahal ini adalah kata kunci dalam ayat. Susunan kalimat juga tidak runut, menyebabkan informasi hukum menjadi rancu dan sebagian terputus.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google menerjemahkan bagian-bagian penting ayat ini secara umum, tetapi ada ketidaksesuaian secara struktur dan istilah. Misalnya, istilah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>kalālah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> tidak muncul sama sekali, padahal ini adalah kata kunci dalam ayat. Susunan kalimat juga tidak runut, menyebabkan informasi hukum menjadi rancu dan sebagian terputus.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Beberapa istilah penting dalam konteks fiqih seperti </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>kalālah, fatwa, dan struktur pembagian waris</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> diterjemahkan secara terlalu umum atau bahkan dihilangkan. Misalnya, </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“mereka meminta fatwa kepadamu”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> hanya diterjemahkan sebagai </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">“mereka meminta pendapat hukum kepadamu,” </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">dan istilah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>kalālah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> tidak disebutkan sama sekali. Hal ini menghilangkan nuansa hukum dan teologis yang menjadi inti dari ayat ini.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Nuansa fatwa, yaitu keputusan hukum yang berasal dari Allah, tidak tergambarkan secara eksplisit. Google hanya menerjemahkan dengan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“memberimu pendapat hukum,”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> yang terdengar umum, tidak menunjukkan kedudukan istimewa dari wahyu ini sebagai fatwa </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>Ilahiyah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.3929487</t>
+  </si>
+  <si>
+    <t>0.4337049</t>
+  </si>
+  <si>
+    <t>0.9587286</t>
   </si>
   <si>
     <t>Dan seandainya mereka benar-benar beriman kepada Allah, Nabi (saw) dan kitab-kitab yang diwahyukan kepadanya, niscaya mereka tidak akan menjadikan keduanya sebagai pemimpin, akan tetapi kebanyakan mereka orang-orang yang fasik.</t>
@@ -151,6 +636,248 @@
     <t>Sekiranya mereka beriman kepada Allah, kepada Nabi (Musa), dan kepada apa yang diturunkan kepadanya (Nabi), niscaya mereka tidak akan mengambil orang-orang musyrikin itu menjadi penolong-penolong, tapi kebanyakan dari mereka adalah orang-orang yang fasik.</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google menggunakan kaliamat </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“keduanya sebagai pemimpin”,</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> sementara versi Kemenag menyebutkan</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “orang musyrik itu sebagai teman setia”. </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Kalimat “keduanya” tidak merujuk secara jelas siapa yang dimaksud, sehingga makna menjadi kabur. Akurasi secara umum bisa diterima, tapi tidak setepat versi Kemenag.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google menggunakan kaliamat </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“keduanya sebagai pemimpin”,</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> sementara versi King Fahd menyebutkan</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “penolong-penolong”. </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Kalimat “keduanya” tidak merujuk secara jelas siapa yang dimaksud, sehingga makna menjadi kabur. Akurasi secara umum bisa diterima, tapi tidak setepat versi King Fahd.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Istilah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“awliya"</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> yang dalam konteks ini bermakna </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“penolong setia”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> atau </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“teman dekat</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>dalam solidaritas ideologis dan agama”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> diterjemahkan Google sebagai </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“pemimpin.”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> Ini terlihat menyempitkan makna aslinya. Padahal, </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>awliya</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> dalam konteks ini menunjukkan hubungan kedekatan yang bersifat ideologis, bukan sekadar kepemimpinan.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Penggunaan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“keduanya”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> tanpa subjek eksplisit dan perubahan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>“awliya”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> menjadi </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“pemimpin”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> membuat ayat kehilangan tekanan retoris terhadap larangan menjadikan orang musyrik sebagai sekutu dalam hal agama.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.587157</t>
+  </si>
+  <si>
+    <t>0.49677634</t>
+  </si>
+  <si>
+    <t>0.8624925</t>
+  </si>
+  <si>
     <t>Mereka merasa puas bersama orang-orang yang tertinggal, dan hati mereka telah dimeteraikan dengan sesuatu, sehingga mereka tidak mengerti.</t>
   </si>
   <si>
@@ -158,6 +885,195 @@
   </si>
   <si>
     <t>Mereka rela berada bersama orang-orang yang tidak pergi berperang, dan hati mereka telah dikunci mati maka mereka tidak mengetahui (kebahagiaan beriman dan berjihad).</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google menerjemahkan bagian utama secara umum benar: </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“Mereka merasa puas bersama orang-orang yang tertinggal”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> mirip dengan Kemenag </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“rela berada bersama orang-orang yang tidak pergi berperang.”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> Namun, Google menghilangkan konteks bahwa yang dimaksud adalah orang-orang yang tidak ikut jihad, bukan sekadar </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“tertinggal.”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Versi terjemahan King Fahd menyebutkan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“orang-orang yang tidak pergi berperang”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, mirip dengan Kemenag, menunjukkan kesamaan dalam keakuratan konteks jihad. Sementara Google justru memberikan kesan pasif atau netral tanpa mengindikasikan bahwa itu bentuk keengganan dari pihak munafik.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Istilah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>“طُبِعَ عَلَىٰ قُلُوبِهِمْ”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> adalah konsep penting tentang penyegelan hati oleh Allah. Google hanya menerjemahkannya sebagai </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“dimeterai dengan sesuatu”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, yang terdengar ambigu dan tidak menyebutkan siapa pelakunya yaitu Allah.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Kejanggalan utama adalah kalimat </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“dengan sesuatu”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> yang terdengar tidak alami dan tampak seperti hasil terjemahan harfiah dari mesin tanpa pemahaman konteks. Selain itu, penggunaan kata </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“tertutup”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> atau </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“dikunci”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> seharusnya lebih tepat daripada </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“dimeteraikan dengan sesuatu”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, yang secara bahasa tidak umum dalam narasi keagamaan berbahasa Indonesia.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.50579774</t>
+  </si>
+  <si>
+    <t>0.49528193</t>
+  </si>
+  <si>
+    <t>0.9690749</t>
   </si>
   <si>
     <t>Dan mereka menangkal azab itu dengan memberi kesaksian empat kali atas nama Allah, bahwa sesungguhnya dia termasuk orang-orang yang berdusta.</t>
@@ -169,6 +1085,255 @@
     <t>Istrinya itu dihindarkan dari hukuman oleh sumpahnya empat kali atas nama Allah; sesungguhnya suaminya itu benar-benar termasuk orang-orang yang dusta.</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google menyebut </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“mereka menangkal azab itu”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> tanpa menyebut subjek jelas siapa </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“mereka”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">, dan menggunakan istilah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“memberi kesaksian empat kali”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, sedangkan versi Kemenag menyatakan lebih gamblang:</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “istri itu terhindar dari hukuman apabila dia bersumpah empat kali”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, yang lebih jelas menjelaskan bahwa subjeknya adalah istri yang membela diri.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Versi King Fahd hampir identik dengan Kemenag, yaitu menggunakan kata </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“sumpah”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> dan menyebut jelas bahwa yang dimaksud adalah istri yang menghindari hukuman. Google hanya menyebut </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“memberi kesaksian empat kali atas nama Allah”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Istilah kunci </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>“li‘an”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> tidak dijelaskan atau dibayangkan sama sekali dalam terjemahan Google. Kata </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“memberi kesaksian”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> kurang tepat menggambarkan praktik sumpah empat kali dalam hukum </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>li‘ān</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">, karena dalam konteks fiqih Islam, istilah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">yahlifu </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">(sumpah) berbeda dengan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>syahadah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> (kesaksian biasa). Versi resmi menggunakan istilah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“sumpah”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> yang lebih sesuai dengan terminologi hukum Islam.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Kalimat</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “menangkal azab itu”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> terkesan seperti ekspresi biasa dan kurang menggambarkan konteks hukum berat seperti hukuman zina (rajam atau had). Sebaliknya, versi Kemenag dan King Fahd menyebutkan bahwa sumpah itu membuatnya </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“terhindar dari hukuman”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, yang memberi bobot hukum dan spiritual lebih jelas.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.369777</t>
+  </si>
+  <si>
+    <t>0.39824682</t>
+  </si>
+  <si>
+    <t>0.8155194</t>
+  </si>
+  <si>
     <t>Dan jika surga itu datang kepada mereka dari daerahnya, kemudian mereka diminta untuk mengujinya, niscaya mereka akan mengujinya, dan mereka tidak akan tinggal di dalamnya kecuali sebentar saja.</t>
   </si>
   <si>
@@ -176,6 +1341,130 @@
   </si>
   <si>
     <t>Kalau (Yaṡrib) diserang dari segala penjuru, kemudian diminta kepada mereka supaya murtad , niscaya mereka mengerjakannya dan mereka tiada akan menunda untuk murtad itu, melainkan dalam waktu yang singkat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terjemahan ini keliru secara makna. Padahal tidak ada konteks tentang surga dalam ayat ini. Yang dimaksud adalah serangan terhadap Madinah (Yasrib) dan permintaan untuk berkhianat atau murtad. Akibatnya, seluruh makna ayat menjadi menyimpang total dari konteks perang dan pengkhianatan.
+</t>
+  </si>
+  <si>
+    <t>King Fahd menyampaikan makna dengan lebih akurat: bahwa bila musuh menyerang dari segala arah dan mereka (orang munafik) diminta untuk melakukan tindakan makar atau murtad, mereka akan melakukannya tanpa ragu.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Kalimat </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">“kemudian mereka diminta untuk mengujinya” </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">seharusnya berkaitan dengan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>fitnah, makar, atau pembelotan</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">, bukan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“pengujian”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> secara netral. Istilah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“surga”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> juga merupakan kesalahan besar dalam penerjemahan kosakata dasar dan konteks. Google Translate gagal memahami konteks historis dan istilah dalam wacana konflik (Perang Ahzab), yang sangat penting dalam ayat ini.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Nuansa </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">kemunafikan, kelemahan iman, dan kesiapan berkhianat </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">yang sangat kuat dalam ayat ini hilang total dalam versi Google. Bahkan, penggantian kata menjadi </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>"surga"</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> mengubah seluruh maksud menjadi berlawanan. Penekanan bahwa mereka tidak akan ragu untuk membelot juga tidak tergambarkan, sehingga kehilangan nilai retoris dan peringatan moral dalam ayat tersebut.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.5602459</t>
+  </si>
+  <si>
+    <t>0.5333402</t>
+  </si>
+  <si>
+    <t>0.84354633</t>
   </si>
   <si>
     <t>Dia akan membimbing mereka dan mengatur urusan mereka dengan benar.</t>
@@ -187,6 +1476,188 @@
     <t>Allah akan memberi pimpinan kepada mereka dan memperbaiki keadaan mereka,</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Terjemahan ini masih dapat diterima secara umum, tetapi terdapat penambahan makna yang tidak ada secara eksplisit dalam teks Arab, yakni kalimat </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">“mengatur urusan mereka dengan benar". </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Kemenag menyampaikan dua poin utama dari ayat ini: Allah akan memberi petunjuk dan memperbaiki keadaan mereka</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Terjemahan ini masih dapat diterima secara umum, tetapi terdapat penambahan makna yang tidak ada secara eksplisit dalam teks Arab, yakni kalimat</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “mengatur urusan mereka dengan benar"</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>. Versi King Fahd menyampaikan dua poin utama dari ayat ini: Allah akan memberi petunjuk dan memperbaiki keadaan mereka</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Istilah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>yahdihim</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> diterjemahkan sebagai </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>membimbing mereka</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">, yang bisa diterima untuk konteks umum, tetapi kurang kuat secara teologis dibandingkan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>memberi petunjuk</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">. Istilah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>yusliḥu balahum</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> diterjemahkan menjadi </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>mengatur urusan mereka dengan benar</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, yang merupakan tafsiran, bukan terjemahan literal.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Makna dasar masih bisa dikenali seperti </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>petunjuk dan perbaikan keadaan</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">, tetapi nuansa spiritual seperti </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>hidayah dari Allah sebagai bentuk kasih sayang-Nya</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> kepada orang-orang yang bertobat serta perbaikan kondisi batin dan lahir tidak tergambar secara utuh dalam versi Google.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.62450266</t>
+  </si>
+  <si>
+    <t>0.56521416</t>
+  </si>
+  <si>
+    <t>0.8343748</t>
+  </si>
+  <si>
     <t>Dan Allah akan memberimu kemenangan besar.</t>
   </si>
   <si>
@@ -194,6 +1665,196 @@
   </si>
   <si>
     <t>dan supaya Allah menolongmu dengan pertolongan yang kuat (banyak).</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Google menyebut</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “Dan Allah akan memberimu kemenangan besar”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> yang secara sederhana namun mengandung tafsir, bukan terjemahan literal. Sementara itu, versi Kemenag menggunakan struktur yang lebih sesuai dengan teks Arab, yakni </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“dan agar Allah menolongmu dengan pertolongan yang kuat (banyak)”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">King Fahd menggunakan struktur dan pilihan kata yang sama persis dengan Kemenag, yaitu </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“supaya Allah menolongmu dengan pertolongan yang kuat (banyak)”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">. Ia tetap mempertahankan struktur </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>li (tujuan)</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> dan makna literal dari </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>nasr</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, serta memperkuat kesan bahwa ini adalah bantuan ilahi, bukan sekadar kemenangan hasil usaha sendiri.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google Translate menyederhanakan makna secara berlebihan dan mengabaikan aspek penting dari istilah kunci dalam konteks wahyu. Istilah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>nasr</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> adalah kata penting dalam teologi Islam, yang berarti </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“pertolongan”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> dari Allah. Google memaknai menjadi </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">“kemenangan” </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>membuat kurang nilai teologisnya dan menggeser makna sedikit.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Kalimat </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“pertolongan yang kuat”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> mengandung makna kekuatan dan kepastian akan dukungan Allah. Google menyederhanakan ini menjadi </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“kemenangan besar”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, yang mengurangi nilai retoris dan spiritualnya. Versi Kemenag dan King Fahd lebih kaya secara konteks, karena mempertahankan hubungan antara bantuan Allah dan kemenangan sebagai akibatnya, bukan sinonimnya.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.55058897</t>
+  </si>
+  <si>
+    <t>0.5629516</t>
+  </si>
+  <si>
+    <t>0.9885328</t>
   </si>
   <si>
     <t>Sesungguhnya orang-orang yang menyeru kamu dari belakang bilik-bilik, kebanyakan mereka tidak dapat berpikir.</t>
@@ -205,6 +1866,138 @@
     <t>Sesungguhnya orang-orang yang memanggil kamu dari luar kamar(mu) kebanyakan mereka tidak mengerti.</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Kemenag memilih kata </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“memanggil”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> yang lebih netral dan umum, sedangkan Google memilih </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“menyeru”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> yang memiliki nuansa lebih keras. Kemenag menyesuaikan makna kontekstual dari </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>ḥujurat</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> sebagai tempat tinggal Nabi, bukan bilik-bilik secara literal versi Google. Google juga menggunakan frasa </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>"tidak dapat berpikir"</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">, sedangkan Kemenag memilih </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>"tidak mengerti".</t>
+    </r>
+  </si>
+  <si>
+    <t>Versi King Fahd hampir identik dengan Kemenag. Terjemahan ini menekankan adab memanggil Nabi dari luar rumahnya dan menyampaikan celaan halus atas tindakan yang kurang sopan tersebut. Google lebih kaku secara bahasa dan tidak menyampaikan nuansa sosial dan adab dalam ayat ini.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google tidak menerjemahkan istilah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>al ḥujurat</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> secara kontekstual. Kata ini tidak sekadar berarti </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“bilik-bilik”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, tapi mengacu pada kamar-kamar istri Nabi yang berada di dekat masjid Nabawi. Dalam konteks keislaman dan sejarah, ini penting.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ayat ini mengandung sindiran halus kepada orang-orang yang kurang sopan terhadap Nabi dengan memanggilnya dari luar kamar. Nuansa ini tidak ditangkap Google. Kemenag dan King Fahd menyampaikan ini dengan lebih halus dan bernuansa. Frasa "memanggil engkau (Muhammad)" dan "tidak mengerti" memberi kesan bahwa mereka tidak memahami adab, bukan sekadar bodoh secara intelektual.</t>
+  </si>
+  <si>
+    <t>0.56849253</t>
+  </si>
+  <si>
+    <t>0.48918647</t>
+  </si>
+  <si>
+    <t>0.8354488</t>
+  </si>
+  <si>
     <t>Mereka berseru kepada orang-orang kafir, “Bukankah kami dahulu bersama kamu?” Mereka menjawab, “Benar, tetapi kamu telah mencobai dirimu sendiri, menanti-nantikan, dan ragu-ragu, dan angan-anganmu itu telah menipu kamu, hingga datanglah keputusan Allah, lalu penipu itu menipu kamu tentang Allah.”</t>
   </si>
   <si>
@@ -212,6 +2005,152 @@
   </si>
   <si>
     <t>Orang-orang munafik itu memanggil mereka (orang-orang mukmin) seraya berkata, "Bukankah kami dahulu bersama-sama dengan kamu?" Mereka menjawab, "Benar, tetapi kamu mencelakakan dirimu sendiri dan menunggu (kehancuran kami), dan kamu ragu-ragu serta ditipu oleh angan-angan kosong sehingga datanglah ketetapan Allah; dan kamu telah ditipu terhadap Allah oleh (setan) yang amat penipu.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Google menerjemahkan:</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> "Mereka berseru kepada orang-orang kafir...". </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Padahal konteks yang tepat, sebagaimana dalam terjemahan Kemenag, adalah:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>"Orang-orang munafik memanggil orang-orang mukmin..."</t>
+    </r>
+  </si>
+  <si>
+    <t>Versi King Fahd menyusun makna dengan sangat mirip dengan Kemenag yaitu menyebut orang-orang munafik sebagai subjek. Terjemahan Google terkesan lebih datar, dan tidak membedakan dengan jelas antara penggambaran kondisi batin orang munafik dan sebab akibat kejatuhan mereka.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">“Mencelakakan dirimu sendiri” </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">diterjemahkan menjadi </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“mencobai dirimu sendiri”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, yang tidak sesuai konteks syar’i.</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “Penipu itu menipu kamu tentang Allah”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> terasa janggal. Kemenag dan King Fahd menjelaskan bahwa yang dimaksud adalah setan, </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“penipu yang sangat besar”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">, bukan hanya </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“penipu”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> tanpa konteks.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Urutan tindakan dalam ayat ini sangat penting sebagai penjelasan mengapa orang-orang munafik binasa. Kemenag dan King Fahd mempertahankan alur retoris tersebut, sementara Google mencampur urutan dan menggunakan diksi yang kurang kuat  seperti </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>"menanti-nantikan"</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> bukanlah kata yang biasa dipakai dalam konteks ancaman ilahi atau penghakiman.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.7552879</t>
+  </si>
+  <si>
+    <t>0.7486117</t>
+  </si>
+  <si>
+    <t>0.93908787</t>
   </si>
   <si>
     <t>Sesungguhnya percakapan diam-diam itu dari setan, agar ia menyusahkan orang-orang yang beriman, dan ia tidak akan membahayakan mereka sedikit pun kecuali dengan izin Allah. Dan hendaklah orang-orang yang beriman bertawakal kepada Allah.</t>
@@ -223,6 +2162,210 @@
     <t>Sesungguhnya pembicaraan rahasia itu adalah dari setan, supaya orang-orang yang beriman itu berduka cita, sedang pembicaraan itu tiadalah memberi mudarat sedikit pun kepada mereka, kecuali dengan izin Allah dan kepada Allah-lah hendaknya orang-orang yang beriman bertawakal.</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google menerjemahkan: </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“Sesungguhnya percakapan diam-diam itu dari setan, agar ia menyusahkan orang-orang yang beriman…”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">. Terjemahan ini cukup dekat, tetapi memiliki kekaburan. Kata </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">“ia” </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>dalam</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “agar ia menyusahkan…”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> tidak jelas merujuk ke siapa. Dalam konteksnya, yang menyusahkan adalah percakapan rahasia itu sebagai bagian dari godaan setan, bukan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“ia”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> sebagai subjek tunggal.</t>
+    </r>
+  </si>
+  <si>
+    <t>King Fahd menyatakan “Pembicaraan rahasia itu dari setan, supaya orang-orang beriman berduka cita…”. Hampir identik dengan versi Kemenag dalam struktur dan makna. Google Translate menyebut “percakapan diam-diam”, yang tidak salah tapi kurang idiomatis dibandingkan “pembicaraan rahasia” seperti dalam versi King Fahd</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Istilah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“percakapan diam-diam”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> untuk </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“najwa”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> terdengar kurang baku dan tidak umum digunakan dalam diskursus teologis. Istilah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“pembicaraan rahasia”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> lebih lazim digunakan dalam konteks tafsir atau penjelasan ayat.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Kemenag dan King Fahd mempertahankan urutan tematis: dari asal pembicaraan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>(setan)</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">, tujuannya </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>(membuat sedih)</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">, ketenangan iman </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>(tidak berbahaya kecuali dengan izin Allah)</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">, hingga penutup dengan anjuran </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>bertawakal</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>. Google memotong alur retoris itu dengan kalimat pendek yang tidak sekuat penekanan versi resmi.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.6769451</t>
+  </si>
+  <si>
+    <t>0.6856599</t>
+  </si>
+  <si>
+    <t>0.9417056</t>
+  </si>
+  <si>
     <t>Bagi orang-orang muhajirin fakir yang telah diusir dari rumah dan harta mereka, karena mereka mencari karunia Allah, keridhaan-Nya, dan karena mereka mendukung Allah dan Rasul-Nya. Mereka itulah orang-orang yang benar.</t>
   </si>
   <si>
@@ -230,6 +2373,164 @@
   </si>
   <si>
     <t>(Juga) bagi para fukara yang berhijrah yang diusir dari kampung halaman dan dari harta benda mereka (karena) mencari karunia dari Allah dan keridaan-Nya dan mereka menolong Allah dan rasul-Nya.  Mereka itulah orang-orang yang benar.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Terjemahan Google cukup dekat secara struktur, tetapi kehilangan kehalusan dan konteks naratif. Misalnya Frasa </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“karena mereka…”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> diulang dua kali oleh Google</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> (“karena mereka mencari… dan karena mereka mendukung…”)</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, terdengar tidak efisien. Kemenag menyambungkan keduanya dengan kata “</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>demi”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, yang lebih halus dan padu.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Struktur King Fahd hampir identik dengan Kemenag dan lebih tepat secara tata bahasa dan idiomatik. Seperti Google menghilangkan konteks </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“(harta rampasan itu juga)”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> yang menjadi bagian penting dari konteks ayat, meskipun tidak eksplisit di dalam teks Arab ayat ini. Penggunaan “fukara” di King Fahd mengisyaratkan istilah asli Arab yang tidak digunakan oleh Google.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">“Mendukung Allah dan Rasul-Nya”. </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Google Translate terdengar seperti konteks politis modern, sedangkan makna aslinya adalah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “menolong agama Allah dan Rasul-Nya”, </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>padahal ini konteks keimanan, bukan sekadar dukungan.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Terjemahan Google terasa datar dan terlalu literal. Hilang kesinambungan narasi antara kondisi</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> fakir-miskin, hijrah, dan perjuangan di jalan Allah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>. Terputus-putus karena dua kali menyebut</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “karena mereka...”,</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> sementara Kemenag dan King Fahd menyajikannya sebagai satu rangkaian amal yang mulia.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.542545</t>
+  </si>
+  <si>
+    <t>0.834056</t>
+  </si>
+  <si>
+    <t>0.6021458</t>
   </si>
   <si>
     <t>Sungguh, telah ada bagimu pada mereka suri teladan yang baik bagi siapa saja yang mengharap rahmat Allah dan hari akhir. Barangsiapa yang berpaling, maka sesungguhnya Allah Maha Kaya lagi Maha Terpuji.</t>
@@ -241,6 +2542,135 @@
     <t>Sesungguhnya pada mereka itu (Ibrāhīm dan umatnya) ada teladan yang baik bagimu; (yaitu) bagi orang-orang yang mengharap (pahala) Allah dan (keselamatan pada) hari kemudian.  Dan barang siapa yang berpaling, maka sesungguhnya Allah Dia-lah yang Maha kaya lagi Maha Terpuji.</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Secara umum akurat. Makna utama tetap tersampaikan, meski Google tidak menyebutkan tokoh </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“Ibrahim dan umatnya”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> secara eksplisit seperti versi Kemenag. Perbedaan hanya pada istilah dan gaya bahasa.</t>
+    </r>
+  </si>
+  <si>
+    <t>Setara dalam makna dasar, namun King Fahd lebih kuat dalam kejelasan subjek dan gaya retoris. Google lebih sederhana dan cenderung literal.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google Translate menerjemahkan istilah penting seperti </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“rahmat Allah”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> dan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“hari akhir”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> dengan cukup tepat secara umum, namun tidak selalu kontekstual. Misalnya, </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">“rahmat” </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">dalam konteks ayat ini lebih tepat jika diterjemahkan sebagai </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“pahala”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> sebagaimana dalam versi Kemenag dan King Fahd. Ketidaktepatan semacam ini dapat memengaruhi pemahaman makna teologis ayat secara utuh.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google kurang mampu mempertahankan kekuatan retoris dan keindahan bahasa ayat. Frasa seperti </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“Dia-lah yang Maha Kaya lagi Maha Terpuji”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> dalam versi resmi memberikan tekanan makna yang lebih kuat dan indah, sedangkan versi Google terdengar lebih netral dan kurang menyentuh sisi emosional atau retoris ayat.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.78537345</t>
+  </si>
+  <si>
+    <t>0.6673583</t>
+  </si>
+  <si>
+    <t>0.90969396</t>
+  </si>
+  <si>
     <t>Hai orang-orang yang beriman, maukah kamu Aku tunjukkan suatu jual beli yang dapat menyelamatkan kamu dari azab yang pedih?</t>
   </si>
   <si>
@@ -248,6 +2678,219 @@
   </si>
   <si>
     <t>Hai orang-orang yang beriman, sukakah kamu aku tunjukkan suatu perniagaan yang dapat menyelamatkanmu dari azab yang pedih?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Google Translate cukup setara dalam menyampaikan makna inti ayat, yaitu ajakan kepada orang beriman untuk mengetahui bentuk</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “jual beli” (ibadah) </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>yang menyelamatkan dari azab. Versi Google menggunakan istilah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “jual beli”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">, sementara Kemenag memilih </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“perdagangan”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> yang terdengar lebih alami dalam konteks bahasa Indonesia.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Versi Google juga mirip dengan King Fahd secara makna. Namun, King Fahd menggunakan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“perniagaan”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> yang memberi kesan lebih formal dan klasik. Secara struktur, King Fahd dan Kemenag lebih selaras dengan gaya bahasa Al-Qur’an dalam bentuk ajakan yang halus dan retoris.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Istilah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“jual beli”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> dalam Google adalah terjemahan literal dari </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>tijarah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">, namun secara teologis, istilah ini dapat menimbulkan pemahaman yang sempit. Dalam konteks ayat, </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>tijarah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> bermakna kiasan: amal atau pengorbanan demi pahala akhirat. Versi Kemenag dan King Fahd lebih tepat dalam menangkap makna kiasan dengan memakai</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “perdagangan”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> atau </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“perniagaan”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google belum mampu menyampaikan nuansa metaforis dari kata </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>tijarah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">. Sementara Kemenag dan King Fahd mengisyaratkan bahwa </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“perdagangan”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> di sini bukan dalam arti harfiah, melainkan sebagai bentuk ibadah dan pengorbanan yang bernilai pahala. Penekanan retoris dalam gaya tanya juga kurang terasa di versi Google dibanding versi resmi.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.75786316</t>
+  </si>
+  <si>
+    <t>0.7706021</t>
+  </si>
+  <si>
+    <t>0.68383336</t>
   </si>
   <si>
     <t>Dan belumlah ada yang menyusul mereka. Dan Dia Maha Perkasa lagi Maha Bijaksana.</t>
@@ -259,6 +2902,175 @@
     <t>dan (juga) kepada kaum yang lain dari mereka yang belum berhubungan dengan mereka.  Dan Dia-lah Yang Maha Perkasa lagi Maha Bijaksana.</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google Translate cukup jauh dari versi Kemenag. Frasa </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“yang menyusul mereka”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> tidak setara dengan makna </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>لَمَّا يَلْحَقُوا بِهِمْ</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>yang dalam konteks ayat berarti "</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">yang belum bergabung/bertemu dengan mereka (secara umat)." </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Kemenag menerjemahkannya lebih tepat dengan</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “belum bertemu dengan mereka”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, menjaga makna konteks sosial dan sejarah.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>King Fahd lebih dekat dengan Kemenag dan secara makna lebih akurat. Frasa</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “belum berhubungan dengan mereka”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> lebih tepat dalam menjelaskan kelompok umat yang belum menerima dakwah langsung. Sementara Google memberi kesan urutan atau kematian </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“menyusul”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> yang salah konteks.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Google Translate kurang akurat dalam menerjemahkan konsep kunci pada ayat ini. Istilah seperti</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve"> يَلْحَقُوا </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>diterjemahkan secara literal sebagai</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “menyusul”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, padahal dalam tafsir, ini merujuk pada kaum lain yang belum menerima risalah atau dakwah. Akibatnya, pemahaman ayat bisa bergeser jauh dari maksud aslinya.</t>
+    </r>
+  </si>
+  <si>
+    <t>Google gagal menangkap konteks bahwa ayat ini berbicara tentang penyebaran risalah Islam kepada kaum setelah generasi sahabat. Nuansa inklusivitas dan janji dakwah kepada umat yang akan datang hilang. Sebaliknya, versi Kemenag dan King Fahd menjaga makna ini dengan lebih baik.</t>
+  </si>
+  <si>
+    <t>0.7801051</t>
+  </si>
+  <si>
+    <t>0.68620974</t>
+  </si>
+  <si>
+    <t>0.8490493</t>
+  </si>
+  <si>
     <t>Dan Allah tidak akan menunda suatu jiwa ketika telah tiba ajalnya. Dan Allah Maha Mengetahui apa yang kamu kerjakan.</t>
   </si>
   <si>
@@ -266,6 +3078,219 @@
   </si>
   <si>
     <t>Dan Allah sekali-kali tidak akan menangguhkan (kematian) seseorang apabila datang waktu kematiannya.  Dan Allah Maha Mengetahui apa yang kamu kerjakan.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Terjemahan Google cukup akurat secara makna dasar. Frasa </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“tidak akan menunda suatu jiwa ketika telah tiba ajalnya”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> setara dengan</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “tidak akan menunda (kematian) seseorang apabila waktu kematiannya telah datang.”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> Namun, Kemenag menggunakan istilah yang lebih jelas dengan menyisipkan kata “kematian” agar makna tidak rancu.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Secara makna, Google hampir sama dengan King Fahd. Namun, King Fahd menambahkan penekanan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“sekali-kali tidak akan menangguhkan”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">, yang memberi kesan lebih tegas dalam bahasa Arab asli </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>(لن يؤخر الله نفساً إذا جاء أجلها)</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>. Sementara Google menerjemahkannya lebih netral dan tidak mengangkat aspek penekanan ini.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Istilah kunci seperti</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve"> أجلها </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">diterjemahkan sebagai </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“ajalnya”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> oleh Google, yang sudah tepat secara istilah teologis. Namun, frasa </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“suatu jiwa”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> untuk نفساً bisa terdengar terlalu literal dan kurang personal dibanding </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“seseorang”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>. Kemenag dan King Fahd lebih berhasil menyampaikan konsep tersebut dengan pilihan kata yang lebih natural dan familiar.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Google Translate cenderung netral dan kehilangan kekuatan retoris dari frasa</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve"> لن يؤخر الله نفساً.</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> Penekanan larangan keras atau kepastian mutlak yang terkandung dalam struktur bahasa Arab tidak sepenuhnya tercermin. Kemenag menggunakan struktur </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“tidak akan menunda (kematian)”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> dan King Fahd dengan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“sekali-kali tidak akan menangguhkan”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> memberi nuansa yang lebih kuat sesuai konteks.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.6563927</t>
+  </si>
+  <si>
+    <t>0.7243382</t>
+  </si>
+  <si>
+    <t>0.91179</t>
   </si>
   <si>
     <t>Dan taatilah Allah dan taatilah Rasul. Tetapi jika kamu berpaling, maka sesungguhnya atas Rasul Kami hanyalah pemberitaan yang nyata.</t>
@@ -277,6 +3302,211 @@
     <t>Dan taatlah kepada Allah dan taatlah kepada rasul-Nya; jika kamu berpaling, sesungguhnya kewajiban rasul Kami hanyalah menyampaikan (amanat Allah) dengan terang.</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google Translate menyampaikan makna inti dengan cukup tepat. Frasa </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“Dan taatilah Allah dan taatilah Rasul”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> setara dengan versi Kemenag. Namun, bagian </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“atas Rasul Kami hanyalah pemberitaan yang nyata”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> terdengar kurang alami dan agak kaku dibanding </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“kewajiban Rasul Kami hanyalah menyampaikan (amanah Allah) dengan terang.”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Secara makna, Google hampir setara dengan King Fahd. Namun, versi King Fahd menggunakan struktur </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“rasul-Nya”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> yang lebih konsisten dengan penggunaan kata ganti dalam Al-Qur’an, sementara Google mempertahankan frasa </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“Rasul Kami”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> yang terdengar lebih literal dan kurang umum dalam konteks bahasa Indonesia Al-Qur’an.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google Translate menangkap istilah teologis utama seperti </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">“taat” </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">dan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“Rasu</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>l” dengan baik. Namun, frasa</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “pemberitaan yang nyata”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> kurang tepat untuk mewakili istilah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve"> البلاغ المبين </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">yang bermakna </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“penyampaian yang terang/jelas”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, khususnya dalam konteks penyampaian risalah kenabian. Versi Kemenag dan King Fahd lebih tepat karena menekankan pada tanggung jawab Rasul menyampaikan amanah, bukan sekadar memberitakan.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Makna umum masih tertangkap, tetapi nuansa penting dalam ayat, bahwa Rasul hanya bertugas menyampaikan risalah secara terang tanpa memaksa umat, tidak tersampaikan sebaik versi Kemenag dan King Fahd. Penggunaan</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “pemberitaan yang nyata”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> oleh Google terdengar datar dan tidak cukup mencerminkan penekanan retoris yang dibawa dalam frasa البلاغ المبين.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.78131294</t>
+  </si>
+  <si>
+    <t>0.7814937</t>
+  </si>
+  <si>
+    <t>0.97870713</t>
+  </si>
+  <si>
     <t>Maka apabila telah sampai masanya, peliharalah mereka dengan cara yang ma'ruf, atau pisahkanlah mereka dengan cara yang ma'ruf. Dan persaksikanlah dua orang laki-laki yang adil dari antara kamu, dan tegakkanlah kesaksian itu karena Allah. Yang demikian itu adalah peringatan bagi siapa pun yang beriman kepada Allah dan Hari Akhir. Dan siapa pun yang bertakwa kepada Allah, niscaya Dia akan memberikan jalan keluar baginya.</t>
   </si>
   <si>
@@ -286,6 +3516,335 @@
     <t>Apabila mereka telah mendekati akhir idahnya, maka rujukilah mereka dengan baik atau lepaskanlah mereka dengan baik dan persaksikanlah dengan dua orang saksi yang adil di antara kamu dan hendaklah kamu tegakkan kesaksian itu karena Allah.  Demikianlah diberi pengajaran dengan itu orang yang beriman kepada Allah dan hari akhirat.  Barang siapa bertakwa kepada Allah, niscaya Dia akan mengadakan baginya jalan keluar.</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google Translate menangkap struktur dan makna umum ayat ini dengan cukup baik, seperti </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“peliharalah mereka dengan cara yang ma'ruf”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> dan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“persaksikanlah dua orang laki-laki yang adil.”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> Namun, frasa </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“peliharalah”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> sebagai terjemahan dari </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>فَأَمْسِكُوهُنَّ</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> kurang tepat karena konteks ayat menunjukkan makna </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>"rujuk"</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> (mengembalikan dalam ikatan pernikahan), bukan sekadar memelihara. Kemenag lebih tepat dengan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>"rujuklah (kembali kepada) mereka".</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">King Fahd setara dengan Kemenag dari sisi kesesuaian istilah dan struktur. Sementara Google Translate menggunakan padanan kata yang dapat dimengerti, tetapi masih terdengar kaku dan kadang tidak sepenuhnya tepat dalam istilah fikih seperti </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“peliharalah”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> atau</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “pisahkanlah”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> yang seharusnya </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“rujuk”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> dan </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“ceraikan.”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google Translate tampak kesulitan dalam menyampaikan istilah hukum pernikahan Islam secara tepat. Misalnya: </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>فَأَمْسِكُوهُنَّ</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “peliharalah”,</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> seharusnya </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">“rujuklah”. </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="14.0"/>
+      </rPr>
+      <t xml:space="preserve">فَسَرِّحُوهُنَّ </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“pisahkanlah”,</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> seharusnya </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“lepaskanlah”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> atau </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“ceraikanlah”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Secara konteks, Google menangkap makna umum, tetapi kurang menggambarkan nuansa fikih dan etika dalam talak yang ditonjolkan di ayat ini. Pilihan kata seperti </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“peliharalah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">” atau </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“pisahkanlah”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> mengaburkan kejelasan hukum tentang talak dan rujuk.
+Penekanan retoris pada </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“tegakkanlah kesaksian itu karena Allah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>” juga kurang kuat karena kata</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “tegakkanlah”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> terdengar formal, tapi tidak menegaskan sisi spiritual dan amanah seperti dalam versi Kemenag dan King Fahd.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.64199346</t>
+  </si>
+  <si>
+    <t>0.58838105</t>
+  </si>
+  <si>
+    <t>0.9486552</t>
+  </si>
+  <si>
     <t>Dan ketika Nabi SAW menceritakan suatu pernyataan kepada salah seorang istrinya, dan ketika istrinya itu menceritakannya, lalu Allah memberitahukannya kepada beliau, beliau pun memberitahukannya sebagian dan mengabaikan sebagian lagi. Ketika Nabi SAW menceritakannya, istrinya bertanya, "Siapa yang memberitahumu tentang ini?" Beliau menjawab, "Yang Maha Mengetahui lagi Maha Mengenal yang memberitahuku."</t>
   </si>
   <si>
@@ -293,6 +3852,218 @@
   </si>
   <si>
     <t>Dan ingatlah ketika nabi membicarakan secara rahasia kepada salah seorang dari istri-istrinya (ῌafṣah) suatu peristiwa.  Maka tatkala (ῌafṣah) menceritakan peristiwa itu (kepada ʻĀ`isyah) dan Allah memberitahukan hal itu (semua pembicaraan ῌafṣah dengan ʻĀ`isyah) kepada Muhammad, lalu Muhammad memberitahukan sebagian (yang diberitakan Allah kepadanya) dan menyembunyikan sebagian yang lain (kepada ῌafṣah).  Maka tatkala (Muhammad) memberitahukan pembicaraan (antara ῌafṣah dan ʻĀ`isyah), lalu ῌafṣah bertanya, "Siapakah yang telah memberitahukan hal ini kepadamu?" Nabi menjawab, "Telah diberitahukan kepadaku oleh Allah yang Maha Mengetahui lagi Maha Mengenal".</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Terjemahan Google cukup baik dalam menangkap struktur naratif ayat. Ia menyampaikan alur peristiwa yang dimulai dari </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>pembicaraan rahasia Nabi SAW, pembocoran oleh istrinya, pemberitahuan Allah, hingga respon istri dan jawaban Nab</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">i. Namun, Kemenag lebih konsisten secara teknis dan terminologis, serta memberikan konteks tambahan seperti menyebut nama </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Hafshah dan Aisyah</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, yang meskipun tidak ada dalam teks, merupakan tafsiran sah dari riwayat sahih.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">King Fahd memberikan terjemahan paling rinci, menjelaskan runtutan dan hubungan antar peristiwa dengan sangat jelas. Penambahan nama istri </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>(ῌafṣah dan Aisyah)</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> juga menunjukkan pendekatan tafsiriyah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>(penafsiran berdasarkan konteks riwayat)</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>. Google tidak memberikan kejelasan itu, meskipun secara garis besar masih bisa dipahami.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Ayat ini tidak mengandung istilah fikih/hukum, tetapi penuh dengan nuansa komunikasi wahyu, kemanusiaan Nabi, dan sifat Allah. Google cukup akurat dalam </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">"Yang Maha Mengetahui lagi Maha Mengenal", </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">setara dengan versi lainnya. Lalu </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“Mengabaikan sebagian lagi”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> sebagai terjemahan dari </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>أَعْرَضَ عَنۡ بَعۡضٍ,</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> kurang tepat. Kata ini lebih mengarah pada </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“tidak menyebutkan”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> atau </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“menyembunyikan”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, bukan</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> “mengabaikan” </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">dalam arti meremehkan atau tidak peduli.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Google menyampaikan makna umum dengan cukup baik, tapi kehilangan nuansa kepekaan dalam </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>tindakan Nabi SAW saat memilih untuk menyembunyikan sebagian informasi</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, yang dalam versi Kemenag dan King Fahd ditonjolkan sebagai kebijaksanaan dan bukan kelengahan.</t>
+    </r>
+  </si>
+  <si>
+    <t>0.74217033</t>
+  </si>
+  <si>
+    <t>0.71028745</t>
+  </si>
+  <si>
+    <t>0.7709818</t>
   </si>
   <si>
     <t>ayat berikut adalah kasus unik dimana skor cosine similarity antar terjemahan manusia (Fahd dan Kemenag) rendah (&lt;0,5)</t>
@@ -316,6 +4087,211 @@
     <t>Dan janganlah sekali-kali orang-orang kafir menyangka, bahwa pemberian tangguh Kami kepada mereka adalah lebih baik bagi mereka.  Sesungguhnya Kami memberi tangguh kepada mereka hanyalah supaya bertambah-tambah dosa mereka; dan bagi mereka azab yang menghinakan.</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Secara garis besar, Google menyampaikan struktur ayat dengan cukup baik, tapi dibanding Kemenag ada kekurangan dalam ketepatan diksi dan nuansa. Beberapa poin : </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“Penangguhan”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> adalah terjemahan literal dari </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>نملي</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">, tetapi tidak sekuat atau seluwes istilah </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>"tenggang waktu"</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> versi Kemenag.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Terjemahan  versi King Fahd </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>"pemberian tangguh"</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> yang lebih idiomatik dan komunikatif dalam konteks bahasa Indonesia.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>“نملي”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">: diterjemahkan sebagai penangguhanو ini bisa diterima secara leksikal, namun kurang komunikatif dan tidak familiar dalam bahasa agama. </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>"Tenggang waktu"</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> (Kemenag) atau </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>"pemberian tangguh"</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> (Fahd) lebih tepat dalam menyampaikan maksud Ilahi untuk mengulur waktu sebagai bentuk </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t>istidraj</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>(menyesatkan melalui kelonggaran).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Ayat ini mengandung makna paradoksal: Allah memberi kelonggaran bukan sebagai kasih sayang, tetapi sebagai bentuk hukuman bertahap</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <i/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> (istidraj)</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">. Versi Google gagal menyampaikan ironi dan retorika tajam ini karena tidak ada penekanan seperti </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“sekali-kali jangan mengira”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> (dari </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>وَلَا يَحْسَبَنَّ)</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>, padahal ini adalah larangan keras terhadap anggapan salah dari orang kafir serta urutan kalimat yang kaku membuat efek retoris hilang.</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">0,502724 </t>
   </si>
   <si>
@@ -328,10 +4304,41 @@
     <t>Nama Ahli Evaluasi</t>
   </si>
   <si>
+    <t>Fakhri Anwar, Lc</t>
+  </si>
+  <si>
     <t>Identifikasi dan Klasifikasi Penyimpangan Makna</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Reduksi Makna Retoris. Seperti ayat yang dimulai dengan bentuk larangan dan penekanan: </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>“jangan sekali-kali mengira”</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">  ini tidak diterjemahkan oleh Google, sehingga kehilangan nada peringatan keras yang sangat penting secara teologis</t>
+    </r>
+  </si>
+  <si>
     <t>Catatan dan Umpan Balik Tambahan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Translate menerjemahkan secara tekstual dan literal. Pendekatan ini cenderung mengabaikan konteks retoris, gaya bahasa Al-Qur’an, dan kekhasan bahasa sastra Arab. Terjemahan manusia (Kemenag &amp; King Fahd) lebih komunikatif dan idiomatik, menjaga nuansa peringatan dan makna tersirat yang seringkali penting dalam pesan ilahi.
+</t>
   </si>
   <si>
     <r>
@@ -414,7 +4421,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -433,6 +4440,12 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -447,6 +4460,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -463,6 +4479,12 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -718,9 +4740,15 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
@@ -744,21 +4772,35 @@
         <v>138.0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+      <c r="F2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
@@ -782,21 +4824,35 @@
         <v>54.0</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="F3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -820,21 +4876,35 @@
         <v>176.0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+      <c r="F4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>41</v>
+      </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -858,21 +4928,35 @@
         <v>81.0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
+      <c r="F5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -896,21 +4980,35 @@
         <v>87.0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
+      <c r="F6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>61</v>
+      </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -934,21 +5032,35 @@
         <v>8.0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
+      <c r="F7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
@@ -972,21 +5084,35 @@
         <v>14.0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
+      <c r="F8" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>81</v>
+      </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -1010,21 +5136,35 @@
         <v>5.0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
+      <c r="F9" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -1048,21 +5188,35 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
+      <c r="F10" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
@@ -1086,21 +5240,35 @@
         <v>4.0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
+      <c r="F11" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>111</v>
+      </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
@@ -1124,21 +5292,35 @@
         <v>14.0</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>40</v>
+        <v>113</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
+      <c r="F12" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>121</v>
+      </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
@@ -1162,21 +5344,35 @@
         <v>10.0</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
+      <c r="F13" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>131</v>
+      </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
@@ -1200,21 +5396,35 @@
         <v>8.0</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>47</v>
+        <v>134</v>
       </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
+      <c r="F14" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>141</v>
+      </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
@@ -1238,21 +5448,35 @@
         <v>6.0</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>49</v>
+        <v>143</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>50</v>
+        <v>144</v>
       </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
+      <c r="F15" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>151</v>
+      </c>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
@@ -1276,21 +5500,35 @@
         <v>10.0</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
+      <c r="F16" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>161</v>
+      </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
@@ -1314,21 +5552,35 @@
         <v>3.0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>55</v>
+        <v>163</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>56</v>
+        <v>164</v>
       </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
+      <c r="F17" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>171</v>
+      </c>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
@@ -1352,21 +5604,35 @@
         <v>11.0</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>58</v>
+        <v>173</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>59</v>
+        <v>174</v>
       </c>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
+      <c r="F18" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>181</v>
+      </c>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
@@ -1390,21 +5656,35 @@
         <v>12.0</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>60</v>
+        <v>182</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>61</v>
+        <v>183</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>62</v>
+        <v>184</v>
       </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
+      <c r="F19" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>191</v>
+      </c>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
@@ -1428,21 +5708,35 @@
         <v>2.0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>63</v>
+        <v>192</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>64</v>
+        <v>193</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>65</v>
+        <v>194</v>
       </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
+      <c r="F20" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>201</v>
+      </c>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
@@ -1466,21 +5760,35 @@
         <v>3.0</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>66</v>
+        <v>202</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>67</v>
+        <v>203</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>68</v>
+        <v>204</v>
       </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
+      <c r="F21" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>211</v>
+      </c>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
@@ -1525,20 +5833,20 @@
       <c r="Z22" s="3"/>
     </row>
     <row r="23">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="7" t="s">
-        <v>69</v>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="9" t="s">
+        <v>212</v>
       </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -1555,41 +5863,41 @@
       <c r="Z23" s="3"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I24" s="9" t="s">
+      <c r="I24" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J24" s="8" t="s">
-        <v>70</v>
+      <c r="J24" s="10" t="s">
+        <v>213</v>
       </c>
-      <c r="K24" s="8" t="s">
-        <v>71</v>
+      <c r="K24" s="10" t="s">
+        <v>214</v>
       </c>
-      <c r="L24" s="8" t="s">
-        <v>72</v>
+      <c r="L24" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
@@ -1607,32 +5915,40 @@
       <c r="Z24" s="3"/>
     </row>
     <row r="25">
-      <c r="A25" s="9">
+      <c r="A25" s="11">
         <v>3.0</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="11">
         <v>178.0</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>73</v>
+      <c r="C25" s="12" t="s">
+        <v>216</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>74</v>
+      <c r="D25" s="12" t="s">
+        <v>217</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>75</v>
+      <c r="E25" s="11" t="s">
+        <v>218</v>
       </c>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="11" t="s">
-        <v>76</v>
+      <c r="F25" s="13" t="s">
+        <v>219</v>
       </c>
-      <c r="K25" s="9">
+      <c r="G25" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="K25" s="11">
         <v>0.592886</v>
       </c>
-      <c r="L25" s="9">
+      <c r="L25" s="11">
         <v>0.478954</v>
       </c>
       <c r="M25" s="3"/>
@@ -1651,18 +5967,18 @@
       <c r="Z25" s="3"/>
     </row>
     <row r="26">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
@@ -1679,18 +5995,18 @@
       <c r="Z26" s="3"/>
     </row>
     <row r="27">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -1707,16 +6023,16 @@
       <c r="Z27" s="3"/>
     </row>
     <row r="28">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -1733,16 +6049,16 @@
       <c r="Z28" s="3"/>
     </row>
     <row r="29">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
@@ -1759,22 +6075,22 @@
       <c r="Z29" s="3"/>
     </row>
     <row r="30">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="15" t="s">
-        <v>77</v>
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="18" t="s">
+        <v>224</v>
       </c>
-      <c r="D30" s="16" t="s">
-        <v>78</v>
+      <c r="D30" s="19" t="s">
+        <v>225</v>
       </c>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
@@ -1791,20 +6107,22 @@
       <c r="Z30" s="3"/>
     </row>
     <row r="31">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="16" t="s">
-        <v>79</v>
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="19" t="s">
+        <v>226</v>
       </c>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
+      <c r="D31" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
@@ -1821,20 +6139,22 @@
       <c r="Z31" s="3"/>
     </row>
     <row r="32">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="16" t="s">
-        <v>80</v>
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="19" t="s">
+        <v>228</v>
       </c>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
+      <c r="D32" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
@@ -1851,20 +6171,22 @@
       <c r="Z32" s="3"/>
     </row>
     <row r="33">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="16" t="s">
-        <v>81</v>
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="19" t="s">
+        <v>230</v>
       </c>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
+      <c r="D33" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
@@ -1881,18 +6203,18 @@
       <c r="Z33" s="3"/>
     </row>
     <row r="34">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
@@ -1909,18 +6231,18 @@
       <c r="Z34" s="3"/>
     </row>
     <row r="35">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
@@ -1937,18 +6259,18 @@
       <c r="Z35" s="3"/>
     </row>
     <row r="36">
-      <c r="A36" s="12"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
@@ -1965,18 +6287,18 @@
       <c r="Z36" s="3"/>
     </row>
     <row r="37">
-      <c r="A37" s="12"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="12"/>
+      <c r="A37" s="15"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
@@ -1995,10 +6317,10 @@
     <row r="38">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
-      <c r="C38" s="18" t="s">
-        <v>82</v>
+      <c r="C38" s="23" t="s">
+        <v>232</v>
       </c>
-      <c r="D38" s="12"/>
+      <c r="D38" s="15"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
@@ -2025,10 +6347,10 @@
     <row r="39">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
-      <c r="C39" s="19" t="s">
-        <v>83</v>
+      <c r="C39" s="24" t="s">
+        <v>233</v>
       </c>
-      <c r="D39" s="12"/>
+      <c r="D39" s="15"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
